--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Params" sheetId="2" r:id="rId2"/>
     <sheet name="Rules" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentManualCount="8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="165">
   <si>
     <t>screenName</t>
   </si>
@@ -313,9 +313,6 @@
     <t>LUXSHOWERSECRETBLISS220ML</t>
   </si>
   <si>
-    <t>BulkDM</t>
-  </si>
-  <si>
     <t>PHSEC001</t>
   </si>
   <si>
@@ -434,6 +431,96 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>VehicleMasterModification2.xlsx</t>
+  </si>
+  <si>
+    <t>Description*</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Registration Number*</t>
+  </si>
+  <si>
+    <t>PHBC009 - BulkDM</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>DISTRIBUTOR_SHUFFLING_UPLOAD</t>
+  </si>
+  <si>
+    <t>Distributor shuffling upload</t>
+  </si>
+  <si>
+    <t>Distributor Shuffling Upload</t>
+  </si>
+  <si>
+    <t>LeopardOBP</t>
+  </si>
+  <si>
+    <t>Liaqat Bazar</t>
+  </si>
+  <si>
+    <t>Ali-Gohar</t>
+  </si>
+  <si>
+    <t>Mohalla General Store</t>
+  </si>
+  <si>
+    <t>DistributorShuffling1.xlsx</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>UPLOAD_ONLY</t>
+  </si>
+  <si>
+    <t>DistributorShuffling2.xlsx</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>User Bulk Upload</t>
+  </si>
+  <si>
+    <t>USER_BULK_UPLOAD</t>
+  </si>
+  <si>
+    <t>Code*</t>
+  </si>
+  <si>
+    <t>Name*</t>
+  </si>
+  <si>
+    <t>Auto_</t>
+  </si>
+  <si>
+    <t>User_</t>
+  </si>
+  <si>
+    <t>UserBulkUpload.xlsx</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SELLING_CATEGORY_BULK_UPLOAD</t>
+  </si>
+  <si>
+    <t>Selling Category Bulk Upload</t>
+  </si>
+  <si>
+    <t>Selling_Category_Bulk_Upload.xlsx</t>
   </si>
 </sst>
 </file>
@@ -457,7 +544,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,6 +560,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -528,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -544,7 +637,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -566,6 +658,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -846,332 +945,432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="23.54296875" customWidth="1"/>
-    <col min="3" max="3" width="28.7265625" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="35.36328125" customWidth="1"/>
     <col min="4" max="4" width="34.6328125" customWidth="1"/>
     <col min="5" max="5" width="39.08984375" customWidth="1"/>
     <col min="6" max="6" width="10.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="B2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="23" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="B3" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="E4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="7" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" s="12" t="s">
+    <row r="5" spans="1:6" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="B13" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="E14" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="B17" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="12" t="s">
+      <c r="E20" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="6" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="12" t="s">
+    <row r="21" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="17" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12" t="s">
+      <c r="E21" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="19" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1183,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="19" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26.6328125" customWidth="1"/>
@@ -1192,8 +1391,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>108</v>
+      <c r="A1" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1207,7 +1406,7 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>55</v>
@@ -1221,7 +1420,7 @@
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -1235,7 +1434,7 @@
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>55</v>
@@ -1249,7 +1448,7 @@
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>55</v>
@@ -1263,7 +1462,7 @@
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>55</v>
@@ -1277,7 +1476,7 @@
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -1286,13 +1485,13 @@
         <v>29</v>
       </c>
       <c r="D7" s="4" t="str">
-        <f ca="1" xml:space="preserve"> TEXT(TODAY() - 6, "yyyy-mm-dd")</f>
-        <v>2025-10-23</v>
+        <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
+        <v>2025-12-06</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -1301,13 +1500,13 @@
         <v>30</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f ca="1">TEXT(TODAY(), "yyyy-mm-dd")</f>
-        <v>2025-10-29</v>
+        <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
+        <v>2025-12-12</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -1316,12 +1515,12 @@
         <v>31</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -1335,7 +1534,7 @@
     </row>
     <row r="11" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>4</v>
@@ -1349,7 +1548,7 @@
     </row>
     <row r="12" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>44</v>
@@ -1358,12 +1557,12 @@
         <v>46</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>44</v>
@@ -1372,12 +1571,12 @@
         <v>47</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>44</v>
@@ -1386,12 +1585,12 @@
         <v>9</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
@@ -1400,12 +1599,12 @@
         <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
@@ -1414,12 +1613,12 @@
         <v>48</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>63</v>
@@ -1428,12 +1627,12 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>63</v>
@@ -1442,12 +1641,12 @@
         <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>65</v>
@@ -1461,7 +1660,7 @@
     </row>
     <row r="20" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>89</v>
@@ -1475,7 +1674,7 @@
     </row>
     <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>89</v>
@@ -1489,7 +1688,7 @@
     </row>
     <row r="22" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>87</v>
@@ -1503,7 +1702,7 @@
     </row>
     <row r="23" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>87</v>
@@ -1515,14 +1714,113 @@
         <v>94</v>
       </c>
     </row>
+    <row r="24" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" t="s">
+        <v>148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24.36328125" customWidth="1"/>
@@ -1533,8 +1831,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>108</v>
+      <c r="A1" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1554,7 +1852,7 @@
     </row>
     <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -1574,7 +1872,7 @@
     </row>
     <row r="3" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>87</v>
@@ -1591,7 +1889,7 @@
     </row>
     <row r="4" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>87</v>
@@ -1608,7 +1906,7 @@
     </row>
     <row r="5" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>87</v>
@@ -1625,7 +1923,7 @@
     </row>
     <row r="6" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>87</v>
@@ -1642,7 +1940,7 @@
     </row>
     <row r="7" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>87</v>
@@ -1656,7 +1954,7 @@
     </row>
     <row r="8" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>49</v>
@@ -1676,7 +1974,7 @@
     </row>
     <row r="9" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>49</v>
@@ -1693,7 +1991,7 @@
     </row>
     <row r="10" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>49</v>
@@ -1710,13 +2008,13 @@
     </row>
     <row r="11" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>41</v>
@@ -1724,13 +2022,13 @@
     </row>
     <row r="12" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>41</v>
@@ -1738,7 +2036,7 @@
     </row>
     <row r="13" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -1758,7 +2056,7 @@
     </row>
     <row r="14" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>4</v>
@@ -1776,7 +2074,7 @@
     </row>
     <row r="15" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -1796,7 +2094,7 @@
     </row>
     <row r="16" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>4</v>
@@ -1810,21 +2108,113 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>5</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>5</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JAR\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="1" r:id="rId1"/>
     <sheet name="Params" sheetId="2" r:id="rId2"/>
     <sheet name="Rules" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" concurrentManualCount="8"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="164">
   <si>
     <t>screenName</t>
   </si>
@@ -338,9 +338,6 @@
   </si>
   <si>
     <t>ProductExclusionFile.xlsx</t>
-  </si>
-  <si>
-    <t>N02N02-Province</t>
   </si>
   <si>
     <t>50250327-0206-KamalOB</t>
@@ -958,7 +955,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -978,7 +975,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -998,10 +995,10 @@
     </row>
     <row r="3" spans="1:6" s="23" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>6</v>
@@ -1013,12 +1010,12 @@
         <v>74</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>87</v>
@@ -1038,7 +1035,7 @@
     </row>
     <row r="5" spans="1:6" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>49</v>
@@ -1058,7 +1055,7 @@
     </row>
     <row r="6" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>44</v>
@@ -1078,7 +1075,7 @@
     </row>
     <row r="7" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>63</v>
@@ -1098,7 +1095,7 @@
     </row>
     <row r="8" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>65</v>
@@ -1118,7 +1115,7 @@
     </row>
     <row r="9" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>68</v>
@@ -1138,7 +1135,7 @@
     </row>
     <row r="10" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>71</v>
@@ -1158,7 +1155,7 @@
     </row>
     <row r="11" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>89</v>
@@ -1178,7 +1175,7 @@
     </row>
     <row r="12" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>100</v>
@@ -1198,7 +1195,7 @@
     </row>
     <row r="13" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>100</v>
@@ -1210,7 +1207,7 @@
         <v>102</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>78</v>
@@ -1218,19 +1215,19 @@
     </row>
     <row r="14" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>125</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>76</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>78</v>
@@ -1238,19 +1235,19 @@
     </row>
     <row r="15" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="C15" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>129</v>
-      </c>
       <c r="D15" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>78</v>
@@ -1258,7 +1255,7 @@
     </row>
     <row r="16" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>28</v>
@@ -1276,7 +1273,7 @@
     </row>
     <row r="17" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>89</v>
@@ -1288,7 +1285,7 @@
         <v>76</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>78</v>
@@ -1296,19 +1293,19 @@
     </row>
     <row r="18" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>76</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>78</v>
@@ -1316,19 +1313,19 @@
     </row>
     <row r="19" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>78</v>
@@ -1336,19 +1333,19 @@
     </row>
     <row r="20" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="C20" s="18" t="s">
         <v>154</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>155</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>75</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>78</v>
@@ -1356,19 +1353,19 @@
     </row>
     <row r="21" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>161</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>162</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F21" s="19" t="s">
         <v>78</v>
@@ -1392,7 +1389,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1406,7 +1403,7 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>55</v>
@@ -1420,7 +1417,7 @@
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>55</v>
@@ -1434,7 +1431,7 @@
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>55</v>
@@ -1448,7 +1445,7 @@
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>55</v>
@@ -1462,7 +1459,7 @@
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>55</v>
@@ -1476,7 +1473,7 @@
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -1486,12 +1483,12 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
-        <v>2025-12-06</v>
+        <v>2025-12-15</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>28</v>
@@ -1501,12 +1498,12 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
-        <v>2025-12-12</v>
+        <v>2025-12-21</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
@@ -1515,12 +1512,12 @@
         <v>31</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -1534,7 +1531,7 @@
     </row>
     <row r="11" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>4</v>
@@ -1548,7 +1545,7 @@
     </row>
     <row r="12" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>44</v>
@@ -1557,12 +1554,12 @@
         <v>46</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>44</v>
@@ -1576,7 +1573,7 @@
     </row>
     <row r="14" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>44</v>
@@ -1585,12 +1582,12 @@
         <v>9</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
@@ -1599,12 +1596,12 @@
         <v>34</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
@@ -1618,7 +1615,7 @@
     </row>
     <row r="17" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>63</v>
@@ -1627,12 +1624,12 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>63</v>
@@ -1646,7 +1643,7 @@
     </row>
     <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>65</v>
@@ -1660,7 +1657,7 @@
     </row>
     <row r="20" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>89</v>
@@ -1674,7 +1671,7 @@
     </row>
     <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>89</v>
@@ -1688,7 +1685,7 @@
     </row>
     <row r="22" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>87</v>
@@ -1702,7 +1699,7 @@
     </row>
     <row r="23" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>87</v>
@@ -1716,7 +1713,7 @@
     </row>
     <row r="24" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>89</v>
@@ -1730,7 +1727,7 @@
     </row>
     <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>89</v>
@@ -1744,10 +1741,10 @@
     </row>
     <row r="26" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>47</v>
@@ -1758,58 +1755,58 @@
     </row>
     <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1832,7 +1829,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1852,7 +1849,7 @@
     </row>
     <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -1872,7 +1869,7 @@
     </row>
     <row r="3" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>87</v>
@@ -1889,7 +1886,7 @@
     </row>
     <row r="4" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>87</v>
@@ -1906,7 +1903,7 @@
     </row>
     <row r="5" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>87</v>
@@ -1923,7 +1920,7 @@
     </row>
     <row r="6" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>87</v>
@@ -1940,7 +1937,7 @@
     </row>
     <row r="7" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>87</v>
@@ -1954,7 +1951,7 @@
     </row>
     <row r="8" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>49</v>
@@ -1974,7 +1971,7 @@
     </row>
     <row r="9" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>49</v>
@@ -1991,7 +1988,7 @@
     </row>
     <row r="10" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>49</v>
@@ -2008,7 +2005,7 @@
     </row>
     <row r="11" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>49</v>
@@ -2022,7 +2019,7 @@
     </row>
     <row r="12" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>49</v>
@@ -2036,7 +2033,7 @@
     </row>
     <row r="13" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -2056,7 +2053,7 @@
     </row>
     <row r="14" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>4</v>
@@ -2074,7 +2071,7 @@
     </row>
     <row r="15" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -2094,7 +2091,7 @@
     </row>
     <row r="16" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>4</v>
@@ -2110,13 +2107,13 @@
     </row>
     <row r="17" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>20</v>
@@ -2127,13 +2124,13 @@
     </row>
     <row r="18" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>20</v>
@@ -2142,18 +2139,18 @@
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>39</v>
@@ -2165,13 +2162,13 @@
     </row>
     <row r="20" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>20</v>
@@ -2180,18 +2177,18 @@
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>20</v>
@@ -2200,15 +2197,15 @@
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>80</v>

--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JAR\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="1" r:id="rId1"/>
@@ -661,7 +661,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -990,7 +990,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="23" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
@@ -1030,7 +1030,7 @@
         <v>59</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1070,7 +1070,7 @@
         <v>61</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1090,7 +1090,7 @@
         <v>64</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1110,7 +1110,7 @@
         <v>67</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1130,7 +1130,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1150,7 +1150,7 @@
         <v>73</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1170,7 +1170,7 @@
         <v>93</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1190,7 +1190,7 @@
         <v>103</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1210,7 +1210,7 @@
         <v>121</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1230,7 +1230,7 @@
         <v>125</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1250,7 +1250,7 @@
         <v>130</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1288,7 +1288,7 @@
         <v>135</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1308,7 +1308,7 @@
         <v>148</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1328,26 +1328,26 @@
         <v>151</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="11" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1355,20 +1355,20 @@
       <c r="A21" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="19" t="s">
-        <v>78</v>
+      <c r="F21" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
-        <v>2025-12-15</v>
+        <v>2026-01-26</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
-        <v>2025-12-21</v>
+        <v>2026-02-01</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huzaifa\JAR\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4095"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="1" r:id="rId1"/>
@@ -943,17 +943,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="31.5703125" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" customWidth="1"/>
-    <col min="3" max="3" width="35.36328125" customWidth="1"/>
-    <col min="4" max="4" width="34.6328125" customWidth="1"/>
-    <col min="5" max="5" width="39.08984375" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" customWidth="1"/>
+    <col min="5" max="5" width="39.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>106</v>
       </c>
@@ -973,7 +973,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" s="6" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>107</v>
       </c>
@@ -990,10 +990,10 @@
         <v>58</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="23" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="23" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>108</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>109</v>
       </c>
@@ -1030,10 +1030,10 @@
         <v>59</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>111</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>112</v>
       </c>
@@ -1070,10 +1070,10 @@
         <v>61</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>113</v>
       </c>
@@ -1090,10 +1090,10 @@
         <v>64</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>114</v>
       </c>
@@ -1110,10 +1110,10 @@
         <v>67</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>115</v>
       </c>
@@ -1130,10 +1130,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>116</v>
       </c>
@@ -1150,10 +1150,10 @@
         <v>73</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>117</v>
       </c>
@@ -1170,10 +1170,10 @@
         <v>93</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>118</v>
       </c>
@@ -1190,10 +1190,10 @@
         <v>103</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>120</v>
       </c>
@@ -1210,10 +1210,10 @@
         <v>121</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>122</v>
       </c>
@@ -1230,10 +1230,10 @@
         <v>125</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>126</v>
       </c>
@@ -1250,10 +1250,10 @@
         <v>130</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>110</v>
       </c>
@@ -1268,10 +1268,10 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>134</v>
       </c>
@@ -1288,10 +1288,10 @@
         <v>135</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>140</v>
       </c>
@@ -1308,10 +1308,10 @@
         <v>148</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="16" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>149</v>
       </c>
@@ -1328,10 +1328,10 @@
         <v>151</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>152</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>160</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>163</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1380,14 +1380,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="19" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="19" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.6328125" customWidth="1"/>
-    <col min="3" max="3" width="21.08984375" customWidth="1"/>
-    <col min="4" max="4" width="41.81640625" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>106</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>108</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>108</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>108</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>108</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>108</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>110</v>
       </c>
@@ -1483,10 +1483,10 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
-        <v>2026-01-26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2026-05-02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -1498,10 +1498,10 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
-        <v>2026-02-01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2026-05-08</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>110</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>107</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>112</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>112</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>112</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>112</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>112</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>113</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>113</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>114</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>117</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>117</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>109</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>109</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>134</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>134</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>140</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>140</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>140</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>140</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>140</v>
       </c>
@@ -1818,16 +1818,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.36328125" customWidth="1"/>
-    <col min="3" max="3" width="22.90625" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>106</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>107</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>109</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>109</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>109</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>109</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>109</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>111</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>111</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>111</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>111</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>111</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>107</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>107</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>107</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>107</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>126</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>134</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>134</v>
       </c>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>152</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>152</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>152</v>
       </c>

--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huzaifa\JAR\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4095"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4100"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="1" r:id="rId1"/>
@@ -943,17 +943,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="31.5703125" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" customWidth="1"/>
-    <col min="5" max="5" width="39.140625" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" customWidth="1"/>
+    <col min="4" max="4" width="34.54296875" customWidth="1"/>
+    <col min="5" max="5" width="39.1796875" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>106</v>
       </c>
@@ -973,7 +973,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>107</v>
       </c>
@@ -993,7 +993,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="23" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="23" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>108</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>109</v>
       </c>
@@ -1030,10 +1030,10 @@
         <v>59</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>111</v>
       </c>
@@ -1050,10 +1050,10 @@
         <v>60</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>112</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>113</v>
       </c>
@@ -1090,10 +1090,10 @@
         <v>64</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>114</v>
       </c>
@@ -1110,10 +1110,10 @@
         <v>67</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>115</v>
       </c>
@@ -1130,10 +1130,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>116</v>
       </c>
@@ -1150,10 +1150,10 @@
         <v>73</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>117</v>
       </c>
@@ -1170,10 +1170,10 @@
         <v>93</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>118</v>
       </c>
@@ -1190,10 +1190,10 @@
         <v>103</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>120</v>
       </c>
@@ -1210,10 +1210,10 @@
         <v>121</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>122</v>
       </c>
@@ -1230,10 +1230,10 @@
         <v>125</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>126</v>
       </c>
@@ -1250,10 +1250,10 @@
         <v>130</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>110</v>
       </c>
@@ -1268,10 +1268,10 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>134</v>
       </c>
@@ -1288,10 +1288,10 @@
         <v>135</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>140</v>
       </c>
@@ -1308,10 +1308,10 @@
         <v>148</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>149</v>
       </c>
@@ -1328,10 +1328,10 @@
         <v>151</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>152</v>
       </c>
@@ -1348,10 +1348,10 @@
         <v>159</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
         <v>160</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>163</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1380,14 +1380,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="19" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" customWidth="1"/>
+    <col min="4" max="4" width="41.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>106</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>108</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>108</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>108</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>108</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>108</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>110</v>
       </c>
@@ -1483,10 +1483,10 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
-        <v>2026-05-02</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2026-05-07</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -1498,10 +1498,10 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
-        <v>2026-05-08</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2026-05-13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>110</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>107</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>112</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>112</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>112</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>112</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>112</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>113</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>113</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>114</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>117</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>117</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>109</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>109</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>134</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>134</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>140</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>140</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>140</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>140</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>140</v>
       </c>
@@ -1818,16 +1818,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="22.81640625" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" customWidth="1"/>
+    <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>106</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>107</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>109</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>109</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>109</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>109</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>109</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>111</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>111</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>111</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>111</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>111</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>107</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>107</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>107</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>107</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>126</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>134</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>134</v>
       </c>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>152</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>152</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>152</v>
       </c>

--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="182">
   <si>
     <t>screenName</t>
   </si>
@@ -518,13 +518,67 @@
   </si>
   <si>
     <t>Selling_Category_Bulk_Upload.xlsx</t>
+  </si>
+  <si>
+    <t>validateMode</t>
+  </si>
+  <si>
+    <t>validateScreenId</t>
+  </si>
+  <si>
+    <t>DYL_202044</t>
+  </si>
+  <si>
+    <t>menuSearch</t>
+  </si>
+  <si>
+    <t>UI_Search</t>
+  </si>
+  <si>
+    <t>dsr profile hq</t>
+  </si>
+  <si>
+    <t>validateGeneratedCol</t>
+  </si>
+  <si>
+    <t>columnId</t>
+  </si>
+  <si>
+    <t>DYL_BG1013</t>
+  </si>
+  <si>
+    <t>Outlet profile HQ</t>
+  </si>
+  <si>
+    <t>rowfilter_TXT__EPP1DESC</t>
+  </si>
+  <si>
+    <t>User profile</t>
+  </si>
+  <si>
+    <t>0201</t>
+  </si>
+  <si>
+    <t>rowfilter_code</t>
+  </si>
+  <si>
+    <t>Vehicle Profile</t>
+  </si>
+  <si>
+    <t>DYL_1032</t>
+  </si>
+  <si>
+    <t>rowfilter_Description</t>
+  </si>
+  <si>
+    <t>rowfilter_TXT__EPP2DESC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,6 +590,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -567,7 +627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -614,11 +674,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -662,6 +731,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.7265625" customWidth="1"/>
@@ -953,7 +1034,7 @@
     <col min="6" max="6" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>106</v>
       </c>
@@ -972,8 +1053,23 @@
       <c r="F1" s="9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G1" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>107</v>
       </c>
@@ -992,8 +1088,23 @@
       <c r="F2" s="11" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" s="23" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G2" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="23" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>108</v>
       </c>
@@ -1013,7 +1124,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>109</v>
       </c>
@@ -1033,7 +1144,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>111</v>
       </c>
@@ -1050,10 +1161,25 @@
         <v>60</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>112</v>
       </c>
@@ -1070,10 +1196,13 @@
         <v>61</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="26"/>
+    </row>
+    <row r="7" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>113</v>
       </c>
@@ -1093,7 +1222,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>114</v>
       </c>
@@ -1113,7 +1242,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>115</v>
       </c>
@@ -1133,7 +1262,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>116</v>
       </c>
@@ -1153,7 +1282,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>117</v>
       </c>
@@ -1173,7 +1302,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>118</v>
       </c>
@@ -1193,7 +1322,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>120</v>
       </c>
@@ -1213,7 +1342,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>122</v>
       </c>
@@ -1233,7 +1362,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>126</v>
       </c>
@@ -1253,7 +1382,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>110</v>
       </c>
@@ -1271,7 +1400,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>134</v>
       </c>
@@ -1282,16 +1411,31 @@
         <v>92</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>135</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>140</v>
       </c>
@@ -1311,7 +1455,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>149</v>
       </c>
@@ -1331,7 +1475,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>152</v>
       </c>
@@ -1348,10 +1492,25 @@
         <v>159</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
         <v>160</v>
       </c>
@@ -1483,7 +1642,7 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
-        <v>2026-05-07</v>
+        <v>2026-05-09</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1498,7 +1657,7 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4100" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="1" r:id="rId1"/>
     <sheet name="Params" sheetId="2" r:id="rId2"/>
     <sheet name="Rules" sheetId="3" r:id="rId3"/>
+    <sheet name="Validations" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="195">
   <si>
     <t>screenName</t>
   </si>
@@ -572,6 +573,45 @@
   </si>
   <si>
     <t>rowfilter_TXT__EPP2DESC</t>
+  </si>
+  <si>
+    <t>Section Creation HQ</t>
+  </si>
+  <si>
+    <t>DYL_202046</t>
+  </si>
+  <si>
+    <t>Section Code</t>
+  </si>
+  <si>
+    <t>rowfilter_TXT__ENTITYCODE</t>
+  </si>
+  <si>
+    <t>AUTOSEC</t>
+  </si>
+  <si>
+    <t>SECTION</t>
+  </si>
+  <si>
+    <t>Distributor Name*</t>
+  </si>
+  <si>
+    <t>Distributor Profile HQ</t>
+  </si>
+  <si>
+    <t>DYL_L__BusinessEntityProfile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULLER &amp; PHIPPS (KORANGI - KARACHI) - </t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>new record</t>
+  </si>
+  <si>
+    <t>update record</t>
   </si>
 </sst>
 </file>
@@ -627,7 +667,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -678,16 +718,33 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -731,18 +788,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1023,18 +1075,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" customWidth="1"/>
-    <col min="3" max="3" width="35.453125" customWidth="1"/>
-    <col min="4" max="4" width="34.54296875" customWidth="1"/>
-    <col min="5" max="5" width="39.1796875" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>106</v>
       </c>
@@ -1053,23 +1108,14 @@
       <c r="F1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H1" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="6" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>107</v>
       </c>
@@ -1088,23 +1134,12 @@
       <c r="F2" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="23" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:9" s="23" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>108</v>
       </c>
@@ -1123,8 +1158,10 @@
       <c r="F3" s="11" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G3" s="27"/>
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>109</v>
       </c>
@@ -1141,10 +1178,12 @@
         <v>59</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G4" s="26"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>111</v>
       </c>
@@ -1163,23 +1202,12 @@
       <c r="F5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>112</v>
       </c>
@@ -1190,19 +1218,20 @@
         <v>45</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>61</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="26"/>
-    </row>
-    <row r="7" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>113</v>
       </c>
@@ -1213,16 +1242,20 @@
         <v>62</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>114</v>
       </c>
@@ -1233,16 +1266,20 @@
         <v>66</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>67</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>115</v>
       </c>
@@ -1259,10 +1296,12 @@
         <v>70</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G9" s="26"/>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>116</v>
       </c>
@@ -1279,10 +1318,12 @@
         <v>73</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>117</v>
       </c>
@@ -1293,16 +1334,22 @@
         <v>92</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>93</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>118</v>
       </c>
@@ -1319,10 +1366,12 @@
         <v>103</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>120</v>
       </c>
@@ -1339,10 +1388,12 @@
         <v>121</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>122</v>
       </c>
@@ -1359,10 +1410,12 @@
         <v>125</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="29"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>126</v>
       </c>
@@ -1379,10 +1432,12 @@
         <v>130</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" s="6" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>110</v>
       </c>
@@ -1397,10 +1452,12 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="G16" s="26"/>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>134</v>
       </c>
@@ -1419,23 +1476,14 @@
       <c r="F17" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="H17" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H17" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>140</v>
       </c>
@@ -1452,10 +1500,12 @@
         <v>148</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="29"/>
+    </row>
+    <row r="19" spans="1:9" s="16" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>149</v>
       </c>
@@ -1472,10 +1522,12 @@
         <v>151</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="29"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>152</v>
       </c>
@@ -1494,23 +1546,12 @@
       <c r="F20" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="H20" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J20" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="K20" s="26" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
         <v>160</v>
       </c>
@@ -1527,8 +1568,10 @@
         <v>163</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>133</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1538,6 +1581,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="19" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1642,7 +1686,7 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
-        <v>2026-05-09</v>
+        <v>2026-06-18</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1657,7 +1701,7 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
-        <v>2026-05-15</v>
+        <v>2026-06-24</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1976,14 +2020,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24.453125" customWidth="1"/>
     <col min="3" max="3" width="22.81640625" customWidth="1"/>
     <col min="4" max="4" width="13.7265625" customWidth="1"/>
     <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" customWidth="1"/>
+    <col min="6" max="6" width="38.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2373,6 +2418,429 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="13.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7265625" customWidth="1"/>
+    <col min="6" max="6" width="24.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ResourcesPK/configPK.xlsx
+++ b/ResourcesPK/configPK.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4100" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Screens" sheetId="1" r:id="rId1"/>
-    <sheet name="Params" sheetId="2" r:id="rId2"/>
-    <sheet name="Rules" sheetId="3" r:id="rId3"/>
-    <sheet name="Validations" sheetId="4" r:id="rId4"/>
+    <sheet name="ScenarioData" sheetId="5" r:id="rId2"/>
+    <sheet name="Params" sheetId="2" r:id="rId3"/>
+    <sheet name="Rules" sheetId="3" r:id="rId4"/>
+    <sheet name="Validations" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="262">
   <si>
     <t>screenName</t>
   </si>
@@ -612,13 +613,215 @@
   </si>
   <si>
     <t>update record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pjp configuration bulk </t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>pjpHeaderBulkCreationExcel.xlsx</t>
+  </si>
+  <si>
+    <t>PJP_HEADER_BULK_CREATION</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Product Code</t>
+  </si>
+  <si>
+    <t>65150683</t>
+  </si>
+  <si>
+    <t>PriceToValidate</t>
+  </si>
+  <si>
+    <t>priceScreenID</t>
+  </si>
+  <si>
+    <t>tradePriceCTN</t>
+  </si>
+  <si>
+    <t>ScreenId</t>
+  </si>
+  <si>
+    <t>PURCHASE_PRICE</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>68453705</t>
+  </si>
+  <si>
+    <t>FieldToValidate</t>
+  </si>
+  <si>
+    <t>Short Description</t>
+  </si>
+  <si>
+    <t>attributeScreenID</t>
+  </si>
+  <si>
+    <t>txt__pprd_abrv</t>
+  </si>
+  <si>
+    <t>DistCode</t>
+  </si>
+  <si>
+    <t>15437620</t>
+  </si>
+  <si>
+    <t>Spending Time</t>
+  </si>
+  <si>
+    <t>TXT__EPP1SPENDINGTIME</t>
+  </si>
+  <si>
+    <t>dsrType</t>
+  </si>
+  <si>
+    <t>Order Booker</t>
+  </si>
+  <si>
+    <t>PJPNO</t>
+  </si>
+  <si>
+    <t>0000000361-JAGUAR PJP OB</t>
+  </si>
+  <si>
+    <t>SELLCAT</t>
+  </si>
+  <si>
+    <t>Full Range Selling Category</t>
+  </si>
+  <si>
+    <t>random</t>
+  </si>
+  <si>
+    <t>OUTLET</t>
+  </si>
+  <si>
+    <t>C0000023667-Shahjalal Super Store</t>
+  </si>
+  <si>
+    <t>0099831</t>
+  </si>
+  <si>
+    <t>QuantityPCS</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>ExpectedMessage</t>
+  </si>
+  <si>
+    <t>SKU 20099831  Quantity Restricted From 500.00000000 To 50000.00000000</t>
+  </si>
+  <si>
+    <t>CompareColumns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Pack, BasePack Description, Lead Base Pack, LeadBasePack Description,status
+</t>
+  </si>
+  <si>
+    <t>Distributor Code*,Selling Category Code*</t>
+  </si>
+  <si>
+    <t>Outlet Code*,Outlet Long Name*</t>
+  </si>
+  <si>
+    <t>PJP HEADER</t>
+  </si>
+  <si>
+    <t>PJP Number*</t>
+  </si>
+  <si>
+    <t>PJP Description*</t>
+  </si>
+  <si>
+    <t>PJP_DESC</t>
+  </si>
+  <si>
+    <t>DSR Code</t>
+  </si>
+  <si>
+    <t>DSR_</t>
+  </si>
+  <si>
+    <t>PJP CREATION HQ</t>
+  </si>
+  <si>
+    <t>DYL_202045</t>
+  </si>
+  <si>
+    <t>PJP</t>
+  </si>
+  <si>
+    <t>DSRGeneratedColumn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSRTestId               </t>
+  </si>
+  <si>
+    <t>DSR Code*</t>
+  </si>
+  <si>
+    <t>PJP_CONFIGURATION_BULK_CREATION</t>
+  </si>
+  <si>
+    <t>pjpConfigurationBulkCreationExcel.xlsx</t>
+  </si>
+  <si>
+    <t>Start Date*</t>
+  </si>
+  <si>
+    <t>PJP Config</t>
+  </si>
+  <si>
+    <t>rowfilter_txt__epjppjpno</t>
+  </si>
+  <si>
+    <t>PJP Header bulk creation</t>
+  </si>
+  <si>
+    <t>PJP Configuration Bulk Creation</t>
+  </si>
+  <si>
+    <t>COMPARE</t>
+  </si>
+  <si>
+    <t>PJPHeaderTestId</t>
+  </si>
+  <si>
+    <t>PJPConfigTestId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PJPHeaderDSRColumn  </t>
+  </si>
+  <si>
+    <t>PJPHeaderGeneratedColumn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PJPNoColumnInConfig  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -640,8 +843,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -663,6 +871,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,7 +958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -795,6 +1009,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1076,17 +1300,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="31.54296875" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -1132,7 +1356,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>168</v>
@@ -1178,7 +1402,7 @@
         <v>59</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G4" s="26"/>
       <c r="H4" s="11"/>
@@ -1200,7 +1424,7 @@
         <v>60</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>168</v>
@@ -1224,7 +1448,7 @@
         <v>61</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>168</v>
@@ -1248,7 +1472,7 @@
         <v>64</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>168</v>
@@ -1272,7 +1496,7 @@
         <v>67</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>168</v>
@@ -1296,7 +1520,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G9" s="26"/>
       <c r="H9" s="11"/>
@@ -1318,9 +1542,11 @@
         <v>73</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="26"/>
+        <v>133</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>256</v>
+      </c>
       <c r="H10" s="11"/>
     </row>
     <row r="11" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -1340,7 +1566,7 @@
         <v>93</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>168</v>
@@ -1366,7 +1592,7 @@
         <v>103</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="11"/>
@@ -1388,7 +1614,7 @@
         <v>121</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="11"/>
@@ -1410,7 +1636,7 @@
         <v>125</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="29"/>
@@ -1432,7 +1658,7 @@
         <v>130</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="11"/>
@@ -1452,7 +1678,7 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="11"/>
@@ -1474,7 +1700,7 @@
         <v>135</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>168</v>
@@ -1500,7 +1726,7 @@
         <v>148</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="29"/>
@@ -1522,7 +1748,7 @@
         <v>151</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="29"/>
@@ -1544,7 +1770,7 @@
         <v>159</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>168</v>
@@ -1568,10 +1794,52 @@
         <v>163</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1580,6 +1848,340 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.90625" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="3" max="3" width="63.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" t="s">
+        <v>247</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B24" t="s">
+        <v>257</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" t="s">
+        <v>260</v>
+      </c>
+      <c r="C28" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" t="s">
+        <v>238</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D30"/>
@@ -1686,7 +2288,7 @@
       </c>
       <c r="D7" s="4" t="str">
         <f ca="1" xml:space="preserve"> TEXT(TODAY() - 4, "yyyy-mm-dd")</f>
-        <v>2026-06-18</v>
+        <v>2026-07-04</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1701,7 +2303,7 @@
       </c>
       <c r="D8" s="5" t="str">
         <f ca="1">TEXT(TODAY()+2, "yyyy-mm-dd")</f>
-        <v>2026-06-24</v>
+        <v>2026-07-10</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2018,10 +2620,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24.453125" customWidth="1"/>
@@ -2031,7 +2633,7 @@
     <col min="6" max="6" width="38.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>106</v>
       </c>
@@ -2051,7 +2653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>107</v>
       </c>
@@ -2071,24 +2673,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>109</v>
       </c>
@@ -2096,7 +2701,7 @@
         <v>87</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>39</v>
@@ -2105,7 +2710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>109</v>
       </c>
@@ -2113,7 +2718,7 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>39</v>
@@ -2122,7 +2727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>109</v>
       </c>
@@ -2130,7 +2735,7 @@
         <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>39</v>
@@ -2139,7 +2744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>109</v>
       </c>
@@ -2147,33 +2752,31 @@
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>111</v>
       </c>
@@ -2181,16 +2784,19 @@
         <v>49</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>111</v>
       </c>
@@ -2198,16 +2804,16 @@
         <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>111</v>
       </c>
@@ -2215,13 +2821,16 @@
         <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>111</v>
       </c>
@@ -2229,33 +2838,27 @@
         <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>107</v>
       </c>
@@ -2263,17 +2866,19 @@
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>107</v>
       </c>
@@ -2281,19 +2886,17 @@
         <v>4</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2">
-        <v>6</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>107</v>
       </c>
@@ -2301,49 +2904,49 @@
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="2">
-        <v>5</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2354,35 +2957,35 @@
         <v>89</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
-      <c r="F19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
@@ -2392,7 +2995,7 @@
         <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>20</v>
@@ -2401,7 +3004,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2412,61 +3015,61 @@
         <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>20</v>
+      </c>
+      <c r="E22" s="2">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="2">
-        <v>5</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>184</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>20</v>
@@ -2475,27 +3078,101 @@
         <v>4</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="2">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="2">
         <v>5</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2503,17 +3180,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="13.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7265625" customWidth="1"/>
+    <col min="4" max="4" width="29.08984375" customWidth="1"/>
+    <col min="5" max="5" width="30.453125" customWidth="1"/>
     <col min="6" max="6" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2765,7 +3442,7 @@
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
         <v>134</v>
       </c>
@@ -2785,7 +3462,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>140</v>
       </c>
@@ -2797,7 +3474,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>149</v>
       </c>
@@ -2809,7 +3486,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>152</v>
       </c>
@@ -2829,7 +3506,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>160</v>
       </c>
@@ -2841,7 +3518,29 @@
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
     </row>
+    <row r="22" spans="1:7" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G22" s="30"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>